--- a/output/casestudy_20260913.xlsx
+++ b/output/casestudy_20260913.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>23.48096840000653</v>
+        <v>22.74357880000025</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>23.66333920000761</v>
+        <v>23.01195770000049</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>15.49812899999961</v>
+        <v>15.05995769999572</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>24.48665930000425</v>
+        <v>23.76390480001282</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>26.31104929999856</v>
+        <v>25.50914840000041</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>20.36951210000552</v>
+        <v>19.81120680000458</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>25.03142429998843</v>
+        <v>24.41191270000127</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>25.19200699999055</v>
+        <v>24.44371689998661</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>34.13966190000065</v>
+        <v>33.18300900000031</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>17.59412399999565</v>
+        <v>17.11719849999645</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>15.05830999999307</v>
+        <v>14.54749450000236</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.5 초</t>
+          <t>22.7 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23.7 초</t>
+          <t>23.0 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15.5 초</t>
+          <t>15.1 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.5 초</t>
+          <t>23.8 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.3 초</t>
+          <t>25.5 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20.4 초</t>
+          <t>19.8 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25.0 초</t>
+          <t>24.4 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25.2 초</t>
+          <t>24.4 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>34.1 초</t>
+          <t>33.2 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17.6 초</t>
+          <t>17.1 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15.1 초</t>
+          <t>14.5 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>265.6 초</t>
+          <t>257.9 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260913.xlsx
+++ b/output/casestudy_20260913.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>22.74357880000025</v>
+        <v>22.76502970000729</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>23.01195770000049</v>
+        <v>23.10870549999527</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>15.05995769999572</v>
+        <v>15.17507689999184</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>23.76390480001282</v>
+        <v>23.83960190000653</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>25.50914840000041</v>
+        <v>25.59141559999262</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>19.81120680000458</v>
+        <v>19.85634329999448</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>24.41191270000127</v>
+        <v>24.63226810000197</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>24.44371689998661</v>
+        <v>24.5923552000022</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>33.18300900000031</v>
+        <v>33.23871580000559</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>17.11719849999645</v>
+        <v>17.20129810000071</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>14.54749450000236</v>
+        <v>14.69049019999511</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22.7 초</t>
+          <t>22.8 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23.0 초</t>
+          <t>23.1 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15.1 초</t>
+          <t>15.2 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.5 초</t>
+          <t>25.6 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19.8 초</t>
+          <t>19.9 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24.4 초</t>
+          <t>24.6 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24.4 초</t>
+          <t>24.6 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17.1 초</t>
+          <t>17.2 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14.5 초</t>
+          <t>14.7 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>257.9 초</t>
+          <t>259.1 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260913.xlsx
+++ b/output/casestudy_20260913.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>22.76502970000729</v>
+        <v>22.74357880000025</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>23.10870549999527</v>
+        <v>23.01195770000049</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>15.17507689999184</v>
+        <v>15.05995769999572</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>23.83960190000653</v>
+        <v>23.76390480001282</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>25.59141559999262</v>
+        <v>25.50914840000041</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>19.85634329999448</v>
+        <v>19.81120680000458</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>24.63226810000197</v>
+        <v>24.41191270000127</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>24.5923552000022</v>
+        <v>24.44371689998661</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>33.23871580000559</v>
+        <v>33.18300900000031</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>17.20129810000071</v>
+        <v>17.11719849999645</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>14.69049019999511</v>
+        <v>14.54749450000236</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22.8 초</t>
+          <t>22.7 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23.1 초</t>
+          <t>23.0 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15.2 초</t>
+          <t>15.1 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.6 초</t>
+          <t>25.5 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19.9 초</t>
+          <t>19.8 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24.6 초</t>
+          <t>24.4 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24.6 초</t>
+          <t>24.4 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17.2 초</t>
+          <t>17.1 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14.7 초</t>
+          <t>14.5 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>259.1 초</t>
+          <t>257.9 초</t>
         </is>
       </c>
     </row>
